--- a/artfynd/A 37040-2026 artfynd.xlsx
+++ b/artfynd/A 37040-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137193150</v>
       </c>
       <c r="B2" t="n">
-        <v>91482</v>
+        <v>91484</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>137190775</v>
       </c>
       <c r="B3" t="n">
-        <v>92806</v>
+        <v>92808</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>137189128</v>
       </c>
       <c r="B8" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
         <v>137189273</v>
       </c>
       <c r="B9" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1608,7 +1608,7 @@
         <v>137189433</v>
       </c>
       <c r="B10" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1728,7 +1728,7 @@
         <v>137189471</v>
       </c>
       <c r="B11" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>137189540</v>
       </c>
       <c r="B12" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         <v>137189990</v>
       </c>
       <c r="B13" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         <v>137190160</v>
       </c>
       <c r="B14" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2210,7 +2210,7 @@
         <v>137190204</v>
       </c>
       <c r="B15" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2330,7 +2330,7 @@
         <v>137190259</v>
       </c>
       <c r="B16" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>137190319</v>
       </c>
       <c r="B17" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2558,7 +2558,7 @@
         <v>137190346</v>
       </c>
       <c r="B18" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
         <v>137190413</v>
       </c>
       <c r="B19" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>137190503</v>
       </c>
       <c r="B20" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
         <v>137190277</v>
       </c>
       <c r="B21" t="n">
-        <v>98236</v>
+        <v>98238</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 37040-2026 artfynd.xlsx
+++ b/artfynd/A 37040-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137193150</v>
       </c>
       <c r="B2" t="n">
-        <v>91484</v>
+        <v>91497</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>137190775</v>
       </c>
       <c r="B3" t="n">
-        <v>92808</v>
+        <v>92821</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>137190200</v>
       </c>
       <c r="B5" t="n">
-        <v>58164</v>
+        <v>58177</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>137189128</v>
       </c>
       <c r="B8" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
         <v>137189273</v>
       </c>
       <c r="B9" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1608,7 +1608,7 @@
         <v>137189433</v>
       </c>
       <c r="B10" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1728,7 +1728,7 @@
         <v>137189471</v>
       </c>
       <c r="B11" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>137189540</v>
       </c>
       <c r="B12" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         <v>137189990</v>
       </c>
       <c r="B13" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         <v>137190160</v>
       </c>
       <c r="B14" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2210,7 +2210,7 @@
         <v>137190204</v>
       </c>
       <c r="B15" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2330,7 +2330,7 @@
         <v>137190259</v>
       </c>
       <c r="B16" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>137190319</v>
       </c>
       <c r="B17" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2558,7 +2558,7 @@
         <v>137190346</v>
       </c>
       <c r="B18" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
         <v>137190413</v>
       </c>
       <c r="B19" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>137190503</v>
       </c>
       <c r="B20" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
         <v>137190277</v>
       </c>
       <c r="B21" t="n">
-        <v>98238</v>
+        <v>98251</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 37040-2026 artfynd.xlsx
+++ b/artfynd/A 37040-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137193150</v>
       </c>
       <c r="B2" t="n">
-        <v>91497</v>
+        <v>91499</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>137190775</v>
       </c>
       <c r="B3" t="n">
-        <v>92821</v>
+        <v>92823</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>137190200</v>
       </c>
       <c r="B5" t="n">
-        <v>58177</v>
+        <v>58179</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>137188373</v>
       </c>
       <c r="B6" t="n">
-        <v>8452</v>
+        <v>8453</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1245,7 +1245,7 @@
         <v>137188874</v>
       </c>
       <c r="B7" t="n">
-        <v>8452</v>
+        <v>8453</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>137189128</v>
       </c>
       <c r="B8" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
         <v>137189273</v>
       </c>
       <c r="B9" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1608,7 +1608,7 @@
         <v>137189433</v>
       </c>
       <c r="B10" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1728,7 +1728,7 @@
         <v>137189471</v>
       </c>
       <c r="B11" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>137189540</v>
       </c>
       <c r="B12" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         <v>137189990</v>
       </c>
       <c r="B13" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         <v>137190160</v>
       </c>
       <c r="B14" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2210,7 +2210,7 @@
         <v>137190204</v>
       </c>
       <c r="B15" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2330,7 +2330,7 @@
         <v>137190259</v>
       </c>
       <c r="B16" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>137190319</v>
       </c>
       <c r="B17" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2558,7 +2558,7 @@
         <v>137190346</v>
       </c>
       <c r="B18" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
         <v>137190413</v>
       </c>
       <c r="B19" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>137190503</v>
       </c>
       <c r="B20" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
         <v>137190277</v>
       </c>
       <c r="B21" t="n">
-        <v>98251</v>
+        <v>98253</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 37040-2026 artfynd.xlsx
+++ b/artfynd/A 37040-2026 artfynd.xlsx
@@ -934,11 +934,7 @@
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -1048,11 +1044,7 @@
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1163,11 +1155,7 @@
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1278,11 +1266,7 @@
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>

--- a/artfynd/A 37040-2026 artfynd.xlsx
+++ b/artfynd/A 37040-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137193150</v>
       </c>
       <c r="B2" t="n">
-        <v>91499</v>
+        <v>91502</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>137190775</v>
       </c>
       <c r="B3" t="n">
-        <v>92823</v>
+        <v>92826</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>137189128</v>
       </c>
       <c r="B8" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>137189273</v>
       </c>
       <c r="B9" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         <v>137189433</v>
       </c>
       <c r="B10" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         <v>137189471</v>
       </c>
       <c r="B11" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1832,7 +1832,7 @@
         <v>137189540</v>
       </c>
       <c r="B12" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>137189990</v>
       </c>
       <c r="B13" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>137190160</v>
       </c>
       <c r="B14" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
         <v>137190204</v>
       </c>
       <c r="B15" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>137190259</v>
       </c>
       <c r="B16" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2428,7 +2428,7 @@
         <v>137190319</v>
       </c>
       <c r="B17" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
         <v>137190346</v>
       </c>
       <c r="B18" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         <v>137190413</v>
       </c>
       <c r="B19" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2766,7 +2766,7 @@
         <v>137190503</v>
       </c>
       <c r="B20" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2880,7 +2880,7 @@
         <v>137190277</v>
       </c>
       <c r="B21" t="n">
-        <v>98253</v>
+        <v>98256</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 37040-2026 artfynd.xlsx
+++ b/artfynd/A 37040-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137193150</v>
       </c>
       <c r="B2" t="n">
-        <v>91502</v>
+        <v>91512</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>137190775</v>
       </c>
       <c r="B3" t="n">
-        <v>92826</v>
+        <v>92836</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>137188221</v>
       </c>
       <c r="B4" t="n">
-        <v>4777</v>
+        <v>4783</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         <v>137190200</v>
       </c>
       <c r="B5" t="n">
-        <v>58179</v>
+        <v>58189</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>137188373</v>
       </c>
       <c r="B6" t="n">
-        <v>8453</v>
+        <v>8459</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>137188874</v>
       </c>
       <c r="B7" t="n">
-        <v>8453</v>
+        <v>8459</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>137189128</v>
       </c>
       <c r="B8" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>137189273</v>
       </c>
       <c r="B9" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         <v>137189433</v>
       </c>
       <c r="B10" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         <v>137189471</v>
       </c>
       <c r="B11" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1832,7 +1832,7 @@
         <v>137189540</v>
       </c>
       <c r="B12" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>137189990</v>
       </c>
       <c r="B13" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>137190160</v>
       </c>
       <c r="B14" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
         <v>137190204</v>
       </c>
       <c r="B15" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>137190259</v>
       </c>
       <c r="B16" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2428,7 +2428,7 @@
         <v>137190319</v>
       </c>
       <c r="B17" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
         <v>137190346</v>
       </c>
       <c r="B18" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         <v>137190413</v>
       </c>
       <c r="B19" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2766,7 +2766,7 @@
         <v>137190503</v>
       </c>
       <c r="B20" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2880,7 +2880,7 @@
         <v>137190277</v>
       </c>
       <c r="B21" t="n">
-        <v>98256</v>
+        <v>98266</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 37040-2026 artfynd.xlsx
+++ b/artfynd/A 37040-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137193150</v>
       </c>
       <c r="B2" t="n">
-        <v>91512</v>
+        <v>91513</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>137190775</v>
       </c>
       <c r="B3" t="n">
-        <v>92836</v>
+        <v>92837</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>137189128</v>
       </c>
       <c r="B8" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>137189273</v>
       </c>
       <c r="B9" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         <v>137189433</v>
       </c>
       <c r="B10" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         <v>137189471</v>
       </c>
       <c r="B11" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1832,7 +1832,7 @@
         <v>137189540</v>
       </c>
       <c r="B12" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>137189990</v>
       </c>
       <c r="B13" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>137190160</v>
       </c>
       <c r="B14" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
         <v>137190204</v>
       </c>
       <c r="B15" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>137190259</v>
       </c>
       <c r="B16" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2428,7 +2428,7 @@
         <v>137190319</v>
       </c>
       <c r="B17" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
         <v>137190346</v>
       </c>
       <c r="B18" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         <v>137190413</v>
       </c>
       <c r="B19" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2766,7 +2766,7 @@
         <v>137190503</v>
       </c>
       <c r="B20" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2880,7 +2880,7 @@
         <v>137190277</v>
       </c>
       <c r="B21" t="n">
-        <v>98266</v>
+        <v>98267</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 37040-2026 artfynd.xlsx
+++ b/artfynd/A 37040-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137193150</v>
       </c>
       <c r="B2" t="n">
-        <v>91513</v>
+        <v>91516</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>137190775</v>
       </c>
       <c r="B3" t="n">
-        <v>92837</v>
+        <v>92840</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         <v>137190200</v>
       </c>
       <c r="B5" t="n">
-        <v>58189</v>
+        <v>58190</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>137189128</v>
       </c>
       <c r="B8" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>137189273</v>
       </c>
       <c r="B9" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         <v>137189433</v>
       </c>
       <c r="B10" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         <v>137189471</v>
       </c>
       <c r="B11" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1832,7 +1832,7 @@
         <v>137189540</v>
       </c>
       <c r="B12" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>137189990</v>
       </c>
       <c r="B13" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>137190160</v>
       </c>
       <c r="B14" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
         <v>137190204</v>
       </c>
       <c r="B15" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>137190259</v>
       </c>
       <c r="B16" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2428,7 +2428,7 @@
         <v>137190319</v>
       </c>
       <c r="B17" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
         <v>137190346</v>
       </c>
       <c r="B18" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         <v>137190413</v>
       </c>
       <c r="B19" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2766,7 +2766,7 @@
         <v>137190503</v>
       </c>
       <c r="B20" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2880,7 +2880,7 @@
         <v>137190277</v>
       </c>
       <c r="B21" t="n">
-        <v>98267</v>
+        <v>98272</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 37040-2026 artfynd.xlsx
+++ b/artfynd/A 37040-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137193150</v>
       </c>
       <c r="B2" t="n">
-        <v>91516</v>
+        <v>91518</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>137190775</v>
       </c>
       <c r="B3" t="n">
-        <v>92840</v>
+        <v>92842</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>137189128</v>
       </c>
       <c r="B8" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>137189273</v>
       </c>
       <c r="B9" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         <v>137189433</v>
       </c>
       <c r="B10" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         <v>137189471</v>
       </c>
       <c r="B11" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1832,7 +1832,7 @@
         <v>137189540</v>
       </c>
       <c r="B12" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>137189990</v>
       </c>
       <c r="B13" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>137190160</v>
       </c>
       <c r="B14" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
         <v>137190204</v>
       </c>
       <c r="B15" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>137190259</v>
       </c>
       <c r="B16" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2428,7 +2428,7 @@
         <v>137190319</v>
       </c>
       <c r="B17" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
         <v>137190346</v>
       </c>
       <c r="B18" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         <v>137190413</v>
       </c>
       <c r="B19" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2766,7 +2766,7 @@
         <v>137190503</v>
       </c>
       <c r="B20" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2880,7 +2880,7 @@
         <v>137190277</v>
       </c>
       <c r="B21" t="n">
-        <v>98272</v>
+        <v>98274</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 37040-2026 artfynd.xlsx
+++ b/artfynd/A 37040-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137193150</v>
       </c>
       <c r="B2" t="n">
-        <v>91518</v>
+        <v>91523</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>137190775</v>
       </c>
       <c r="B3" t="n">
-        <v>92842</v>
+        <v>92847</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         <v>137190200</v>
       </c>
       <c r="B5" t="n">
-        <v>58190</v>
+        <v>58191</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>137189128</v>
       </c>
       <c r="B8" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>137189273</v>
       </c>
       <c r="B9" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         <v>137189433</v>
       </c>
       <c r="B10" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         <v>137189471</v>
       </c>
       <c r="B11" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1832,7 +1832,7 @@
         <v>137189540</v>
       </c>
       <c r="B12" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>137189990</v>
       </c>
       <c r="B13" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>137190160</v>
       </c>
       <c r="B14" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
         <v>137190204</v>
       </c>
       <c r="B15" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>137190259</v>
       </c>
       <c r="B16" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2428,7 +2428,7 @@
         <v>137190319</v>
       </c>
       <c r="B17" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
         <v>137190346</v>
       </c>
       <c r="B18" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         <v>137190413</v>
       </c>
       <c r="B19" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2766,7 +2766,7 @@
         <v>137190503</v>
       </c>
       <c r="B20" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2880,7 +2880,7 @@
         <v>137190277</v>
       </c>
       <c r="B21" t="n">
-        <v>98274</v>
+        <v>98280</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 37040-2026 artfynd.xlsx
+++ b/artfynd/A 37040-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137193150</v>
       </c>
       <c r="B2" t="n">
-        <v>91523</v>
+        <v>91535</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>137190775</v>
       </c>
       <c r="B3" t="n">
-        <v>92847</v>
+        <v>92859</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>137189128</v>
       </c>
       <c r="B8" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>137189273</v>
       </c>
       <c r="B9" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         <v>137189433</v>
       </c>
       <c r="B10" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         <v>137189471</v>
       </c>
       <c r="B11" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1832,7 +1832,7 @@
         <v>137189540</v>
       </c>
       <c r="B12" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>137189990</v>
       </c>
       <c r="B13" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>137190160</v>
       </c>
       <c r="B14" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
         <v>137190204</v>
       </c>
       <c r="B15" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>137190259</v>
       </c>
       <c r="B16" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2428,7 +2428,7 @@
         <v>137190319</v>
       </c>
       <c r="B17" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
         <v>137190346</v>
       </c>
       <c r="B18" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         <v>137190413</v>
       </c>
       <c r="B19" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2766,7 +2766,7 @@
         <v>137190503</v>
       </c>
       <c r="B20" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2880,7 +2880,7 @@
         <v>137190277</v>
       </c>
       <c r="B21" t="n">
-        <v>98280</v>
+        <v>98292</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 37040-2026 artfynd.xlsx
+++ b/artfynd/A 37040-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137193150</v>
       </c>
       <c r="B2" t="n">
-        <v>91535</v>
+        <v>91536</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>137190775</v>
       </c>
       <c r="B3" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>137189128</v>
       </c>
       <c r="B8" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>137189273</v>
       </c>
       <c r="B9" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         <v>137189433</v>
       </c>
       <c r="B10" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         <v>137189471</v>
       </c>
       <c r="B11" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1832,7 +1832,7 @@
         <v>137189540</v>
       </c>
       <c r="B12" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>137189990</v>
       </c>
       <c r="B13" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>137190160</v>
       </c>
       <c r="B14" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
         <v>137190204</v>
       </c>
       <c r="B15" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>137190259</v>
       </c>
       <c r="B16" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2428,7 +2428,7 @@
         <v>137190319</v>
       </c>
       <c r="B17" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
         <v>137190346</v>
       </c>
       <c r="B18" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         <v>137190413</v>
       </c>
       <c r="B19" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2766,7 +2766,7 @@
         <v>137190503</v>
       </c>
       <c r="B20" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2880,7 +2880,7 @@
         <v>137190277</v>
       </c>
       <c r="B21" t="n">
-        <v>98292</v>
+        <v>98293</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 37040-2026 artfynd.xlsx
+++ b/artfynd/A 37040-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137193150</v>
       </c>
       <c r="B2" t="n">
-        <v>91536</v>
+        <v>91539</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>137190775</v>
       </c>
       <c r="B3" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>137189128</v>
       </c>
       <c r="B8" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>137189273</v>
       </c>
       <c r="B9" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         <v>137189433</v>
       </c>
       <c r="B10" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         <v>137189471</v>
       </c>
       <c r="B11" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1832,7 +1832,7 @@
         <v>137189540</v>
       </c>
       <c r="B12" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>137189990</v>
       </c>
       <c r="B13" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>137190160</v>
       </c>
       <c r="B14" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
         <v>137190204</v>
       </c>
       <c r="B15" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>137190259</v>
       </c>
       <c r="B16" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2428,7 +2428,7 @@
         <v>137190319</v>
       </c>
       <c r="B17" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
         <v>137190346</v>
       </c>
       <c r="B18" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         <v>137190413</v>
       </c>
       <c r="B19" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2766,7 +2766,7 @@
         <v>137190503</v>
       </c>
       <c r="B20" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2880,7 +2880,7 @@
         <v>137190277</v>
       </c>
       <c r="B21" t="n">
-        <v>98293</v>
+        <v>98296</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 37040-2026 artfynd.xlsx
+++ b/artfynd/A 37040-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137193150</v>
       </c>
       <c r="B2" t="n">
-        <v>91539</v>
+        <v>91543</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>137190775</v>
       </c>
       <c r="B3" t="n">
-        <v>92863</v>
+        <v>92867</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         <v>137190200</v>
       </c>
       <c r="B5" t="n">
-        <v>58191</v>
+        <v>58194</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>137189128</v>
       </c>
       <c r="B8" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>137189273</v>
       </c>
       <c r="B9" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         <v>137189433</v>
       </c>
       <c r="B10" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         <v>137189471</v>
       </c>
       <c r="B11" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1832,7 +1832,7 @@
         <v>137189540</v>
       </c>
       <c r="B12" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>137189990</v>
       </c>
       <c r="B13" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>137190160</v>
       </c>
       <c r="B14" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
         <v>137190204</v>
       </c>
       <c r="B15" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>137190259</v>
       </c>
       <c r="B16" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2428,7 +2428,7 @@
         <v>137190319</v>
       </c>
       <c r="B17" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
         <v>137190346</v>
       </c>
       <c r="B18" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         <v>137190413</v>
       </c>
       <c r="B19" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2766,7 +2766,7 @@
         <v>137190503</v>
       </c>
       <c r="B20" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2880,7 +2880,7 @@
         <v>137190277</v>
       </c>
       <c r="B21" t="n">
-        <v>98296</v>
+        <v>98300</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
